--- a/excelAvancado/aula03/Atividade1 - Correção.xlsx
+++ b/excelAvancado/aula03/Atividade1 - Correção.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\excelAvancado\aula03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5129B2-93D2-46ED-A572-81C48209B7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11A7918-5045-48C9-A6B7-34BEA3B05118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1B84F655-7CFC-4B36-B908-0234E9DA85DA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{1B84F655-7CFC-4B36-B908-0234E9DA85DA}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="36">
   <si>
     <t>Pedido</t>
   </si>
@@ -289,7 +289,1591 @@
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="216">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -461,7 +2045,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[JAIME DE JESUS ALBUNIO.xlsx]DASHBOARD!Tabela dinâmica2</c:name>
+    <c:name>[Atividade1 - Correção.xlsx]DASHBOARD!Tabela dinâmica2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -689,47 +2273,23 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>DASHBOARD!$W$6:$W$11</c:f>
+              <c:f>DASHBOARD!$W$6:$W$7</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Região Centro-Oeste</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Região Nordeste</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Região Norte</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Região Sudeste</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Região Sul</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DASHBOARD!$X$6:$X$11</c:f>
+              <c:f>DASHBOARD!$X$6:$X$7</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>38675</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>27925</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>12900</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>106480</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>59375</c:v>
+                  <c:v>550</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -945,7 +2505,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[JAIME DE JESUS ALBUNIO.xlsx]DASHBOARD!Tabela dinâmica3</c:name>
+    <c:name>[Atividade1 - Correção.xlsx]DASHBOARD!Tabela dinâmica3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1070,59 +2630,23 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>DASHBOARD!$Z$6:$Z$13</c:f>
+              <c:f>DASHBOARD!$Z$6:$Z$7</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Monitor OLED 33"</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>Pen Drive 32GB</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Smartphone Android</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Smartphone iOS</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>SmartTV TV 50" 4K</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>TV 48" 4K</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>TV 60" 4K</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DASHBOARD!$AA$6:$AA$13</c:f>
+              <c:f>DASHBOARD!$AA$6:$AA$7</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>55845</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>745</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>32200</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>83145</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23730</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>11400</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38290</c:v>
+                  <c:v>550</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1365,7 +2889,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[JAIME DE JESUS ALBUNIO.xlsx]DASHBOARD!Tabela dinâmica4</c:name>
+    <c:name>[Atividade1 - Correção.xlsx]DASHBOARD!Tabela dinâmica4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1628,47 +3152,29 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>DASHBOARD!$AC$6:$AC$11</c:f>
+              <c:f>DASHBOARD!$AC$6:$AC$8</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>17/11/2024</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18/11/2024</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>19/11/2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>20/11/2024</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>21/11/2024</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DASHBOARD!$AD$6:$AD$11</c:f>
+              <c:f>DASHBOARD!$AD$6:$AD$8</c:f>
               <c:numCache>
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>50110</c:v>
+                  <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23565</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>38355</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>71800</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>61525</c:v>
+                  <c:v>330</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3608,158 +5114,30 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45545C52-5F4A-4B2F-9F68-480F42E83C02}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="W5:X11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BB7E321-12A9-40EF-9B68-A41B932CD9BD}" name="Tabela dinâmica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="AC5:AD8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
         <item x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="8">
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de Total" fld="8" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="5">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BB7E321-12A9-40EF-9B68-A41B932CD9BD}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="AC5:AD11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3781,21 +5159,12 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="3">
     <i>
       <x/>
     </i>
     <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
       <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -3808,26 +5177,26 @@
     <dataField name="Soma de Total" fld="8" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="11">
+    <format dxfId="203">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="202">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="201">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="200">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="199">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="198">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3914,31 +5283,31 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B36A23B1-1B29-4DC4-B43D-14CA667403A4}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="Z5:AA13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B36A23B1-1B29-4DC4-B43D-14CA667403A4}" name="Tabela dinâmica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="Z5:AA7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
         <item x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="8">
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="6"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3960,27 +5329,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -3993,31 +5344,147 @@
     <dataField name="Soma de Total" fld="8" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="17">
+    <format dxfId="209">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="208">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="207">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="206">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="205">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="204">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45545C52-5F4A-4B2F-9F68-480F42E83C02}" name="Tabela dinâmica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="W5:X7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de Total" fld="8" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="215">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="214">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="213">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="212">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="211">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="210">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4049,11 +5516,11 @@
   <data>
     <tabular pivotCacheId="1083285153">
       <items count="5">
-        <i x="0" s="1"/>
-        <i x="3" s="1"/>
+        <i x="3"/>
         <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="4" s="1" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="4" nd="1"/>
+        <i x="2" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -4070,13 +5537,13 @@
   <data>
     <tabular pivotCacheId="1083285153">
       <items count="7">
-        <i x="2" s="1"/>
+        <i x="2"/>
         <i x="1" s="1"/>
-        <i x="4" s="1"/>
-        <i x="0" s="1"/>
-        <i x="3" s="1"/>
-        <i x="5" s="1" nd="1"/>
-        <i x="6" s="1" nd="1"/>
+        <i x="4"/>
+        <i x="0"/>
+        <i x="3"/>
+        <i x="5"/>
+        <i x="6"/>
       </items>
     </tabular>
   </data>
@@ -5515,12 +6982,12 @@
     <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.65">
@@ -5713,24 +7180,24 @@
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
       <c r="W6" s="10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="X6" s="9">
-        <v>38675</v>
+        <v>550</v>
       </c>
       <c r="Y6" s="7"/>
       <c r="Z6" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA6" s="9">
-        <v>55845</v>
+        <v>550</v>
       </c>
       <c r="AB6" s="7"/>
       <c r="AC6" s="8">
         <v>45613</v>
       </c>
       <c r="AD6" s="9">
-        <v>50110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
@@ -5757,24 +7224,24 @@
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="X7" s="9">
-        <v>27925</v>
+        <v>550</v>
       </c>
       <c r="Y7" s="7"/>
       <c r="Z7" s="10" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AA7" s="9">
-        <v>745</v>
+        <v>550</v>
       </c>
       <c r="AB7" s="7"/>
       <c r="AC7" s="8">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="AD7" s="9">
-        <v>23565</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
@@ -5800,25 +7267,13 @@
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
-      <c r="W8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="X8" s="9">
-        <v>12900</v>
-      </c>
       <c r="Y8" s="7"/>
-      <c r="Z8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>32200</v>
-      </c>
       <c r="AB8" s="7"/>
-      <c r="AC8" s="8">
-        <v>45615</v>
+      <c r="AC8" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="AD8" s="9">
-        <v>38355</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
@@ -5844,26 +7299,8 @@
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
-      <c r="W9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="X9" s="9">
-        <v>106480</v>
-      </c>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>83145</v>
-      </c>
       <c r="AB9" s="7"/>
-      <c r="AC9" s="8">
-        <v>45616</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>71800</v>
-      </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
@@ -5888,26 +7325,8 @@
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
-      <c r="W10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="X10" s="9">
-        <v>59375</v>
-      </c>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA10" s="9">
-        <v>23730</v>
-      </c>
       <c r="AB10" s="7"/>
-      <c r="AC10" s="8">
-        <v>45617</v>
-      </c>
-      <c r="AD10" s="9">
-        <v>61525</v>
-      </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
@@ -5932,26 +7351,8 @@
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
-      <c r="W11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="X11" s="9">
-        <v>245355</v>
-      </c>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA11" s="9">
-        <v>11400</v>
-      </c>
       <c r="AB11" s="7"/>
-      <c r="AC11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>245355</v>
-      </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
@@ -5979,12 +7380,6 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
-      <c r="Z12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA12" s="9">
-        <v>38290</v>
-      </c>
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
       <c r="AD12" s="7"/>
@@ -6015,12 +7410,6 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA13" s="9">
-        <v>245355</v>
-      </c>
       <c r="AB13" s="7"/>
       <c r="AC13" s="7"/>
       <c r="AD13" s="7"/>
@@ -7427,23 +8816,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="9a771ab8-9434-468b-b9f9-670f3b6d25f4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009FB2177CD81C1A4DBE21E983BA07A47C" ma:contentTypeVersion="5" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ccd9fba292455b7ca710bfc1a35850ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9a771ab8-9434-468b-b9f9-670f3b6d25f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e800c226bc9490fba76dac7ab93073ee" ns3:_="">
     <xsd:import namespace="9a771ab8-9434-468b-b9f9-670f3b6d25f4"/>
@@ -7593,31 +8965,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CDF7E0C-9FA5-45BA-9364-7B3F44FC1777}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a771ab8-9434-468b-b9f9-670f3b6d25f4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929F9EE6-ECFD-44BE-96A1-E7D770E1A88B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9a771ab8-9434-468b-b9f9-670f3b6d25f4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE8E182A-0041-4C02-B81D-230A272881A2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7633,4 +8998,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929F9EE6-ECFD-44BE-96A1-E7D770E1A88B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CDF7E0C-9FA5-45BA-9364-7B3F44FC1777}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a771ab8-9434-468b-b9f9-670f3b6d25f4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>